--- a/孟加拉数据梳理_Erin_20260624.xlsx
+++ b/孟加拉数据梳理_Erin_20260624.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="popular sell" sheetId="1" r:id="rId1"/>
@@ -5717,8 +5717,8 @@
       <c r="Q17" s="17">
         <v>12000</v>
       </c>
-      <c r="R17" s="7" t="s">
-        <v>29</v>
+      <c r="R17" t="s">
+        <v>38</v>
       </c>
       <c r="S17" s="7" t="s">
         <v>87</v>
@@ -6182,8 +6182,8 @@
       <c r="Q26" s="17">
         <v>12000</v>
       </c>
-      <c r="R26" s="7" t="s">
-        <v>29</v>
+      <c r="R26" t="s">
+        <v>38</v>
       </c>
       <c r="S26" s="7" t="s">
         <v>102</v>
@@ -6387,8 +6387,8 @@
       <c r="Q30" s="17">
         <v>12000</v>
       </c>
-      <c r="R30" s="7" t="s">
-        <v>29</v>
+      <c r="R30" t="s">
+        <v>38</v>
       </c>
       <c r="S30" s="7" t="s">
         <v>87</v>
@@ -6489,8 +6489,8 @@
       <c r="Q32" s="17">
         <v>12000</v>
       </c>
-      <c r="R32" s="7" t="s">
-        <v>29</v>
+      <c r="R32" t="s">
+        <v>38</v>
       </c>
       <c r="S32" s="7" t="s">
         <v>134</v>
@@ -6540,8 +6540,8 @@
       <c r="Q33" s="17">
         <v>12000</v>
       </c>
-      <c r="R33" s="7" t="s">
-        <v>29</v>
+      <c r="R33" t="s">
+        <v>38</v>
       </c>
       <c r="S33" s="7" t="s">
         <v>134</v>
@@ -6746,8 +6746,8 @@
       <c r="Q37" s="17">
         <v>12000</v>
       </c>
-      <c r="R37" s="7" t="s">
-        <v>29</v>
+      <c r="R37" t="s">
+        <v>38</v>
       </c>
       <c r="S37" s="7" t="s">
         <v>134</v>
@@ -6797,8 +6797,8 @@
       <c r="Q38" s="17">
         <v>12000</v>
       </c>
-      <c r="R38" s="7" t="s">
-        <v>29</v>
+      <c r="R38" t="s">
+        <v>38</v>
       </c>
       <c r="S38" s="7" t="s">
         <v>134</v>
@@ -6899,8 +6899,8 @@
       <c r="Q40" s="17">
         <v>12000</v>
       </c>
-      <c r="R40" s="7" t="s">
-        <v>29</v>
+      <c r="R40" t="s">
+        <v>38</v>
       </c>
       <c r="S40" s="7" t="s">
         <v>134</v>
@@ -6950,8 +6950,8 @@
       <c r="Q41" s="17">
         <v>12000</v>
       </c>
-      <c r="R41" s="7" t="s">
-        <v>29</v>
+      <c r="R41" t="s">
+        <v>38</v>
       </c>
       <c r="S41" s="7" t="s">
         <v>134</v>
@@ -7208,8 +7208,8 @@
       <c r="Q46" s="17">
         <v>12000</v>
       </c>
-      <c r="R46" s="7" t="s">
-        <v>29</v>
+      <c r="R46" t="s">
+        <v>38</v>
       </c>
       <c r="S46" s="7" t="s">
         <v>134</v>
@@ -10325,7 +10325,7 @@
         <v>12000</v>
       </c>
       <c r="R12" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S12" s="7" t="s">
         <v>134</v>
@@ -10378,7 +10378,7 @@
         <v>12000</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S13" s="7" t="s">
         <v>134</v>
@@ -10431,7 +10431,7 @@
         <v>12000</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S14" s="7" t="s">
         <v>134</v>
@@ -10484,7 +10484,7 @@
         <v>12000</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S15" s="7" t="s">
         <v>134</v>
@@ -10537,7 +10537,7 @@
         <v>12000</v>
       </c>
       <c r="R16" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S16" s="7" t="s">
         <v>134</v>
@@ -10590,7 +10590,7 @@
         <v>12000</v>
       </c>
       <c r="R17" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S17" s="7" t="s">
         <v>134</v>
@@ -10643,7 +10643,7 @@
         <v>12000</v>
       </c>
       <c r="R18" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S18" s="7" t="s">
         <v>134</v>
@@ -10696,7 +10696,7 @@
         <v>12000</v>
       </c>
       <c r="R19" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S19" s="7" t="s">
         <v>134</v>
@@ -10749,7 +10749,7 @@
         <v>12000</v>
       </c>
       <c r="R20" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S20" s="7" t="s">
         <v>134</v>
@@ -10802,7 +10802,7 @@
         <v>12000</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S21" s="7" t="s">
         <v>134</v>
@@ -11371,7 +11371,7 @@
         <v>12000</v>
       </c>
       <c r="R32" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S32" s="7" t="s">
         <v>102</v>
@@ -11422,7 +11422,7 @@
         <v>12000</v>
       </c>
       <c r="R33" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S33" s="7" t="s">
         <v>102</v>
@@ -11473,7 +11473,7 @@
         <v>12000</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S34" s="7" t="s">
         <v>102</v>
@@ -11526,7 +11526,7 @@
         <v>12000</v>
       </c>
       <c r="R35" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S35" s="7" t="s">
         <v>102</v>
@@ -11577,7 +11577,7 @@
         <v>12000</v>
       </c>
       <c r="R36" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S36" s="7" t="s">
         <v>102</v>
@@ -11628,7 +11628,7 @@
         <v>12000</v>
       </c>
       <c r="R37" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S37" s="7" t="s">
         <v>102</v>
@@ -11679,7 +11679,7 @@
         <v>12000</v>
       </c>
       <c r="R38" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S38" s="7" t="s">
         <v>102</v>
@@ -11730,7 +11730,7 @@
         <v>12000</v>
       </c>
       <c r="R39" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S39" s="7" t="s">
         <v>102</v>
@@ -11781,7 +11781,7 @@
         <v>12000</v>
       </c>
       <c r="R40" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S40" s="7" t="s">
         <v>102</v>
@@ -11832,7 +11832,7 @@
         <v>12000</v>
       </c>
       <c r="R41" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S41" s="7" t="s">
         <v>102</v>
@@ -12401,7 +12401,7 @@
         <v>12000</v>
       </c>
       <c r="R52" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S52" s="7" t="s">
         <v>102</v>
@@ -12453,7 +12453,7 @@
         <v>12000</v>
       </c>
       <c r="R53" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S53" s="7" t="s">
         <v>102</v>
@@ -12505,7 +12505,7 @@
         <v>12000</v>
       </c>
       <c r="R54" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S54" s="7" t="s">
         <v>102</v>
@@ -12557,7 +12557,7 @@
         <v>12000</v>
       </c>
       <c r="R55" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S55" s="7" t="s">
         <v>102</v>
@@ -12609,7 +12609,7 @@
         <v>12000</v>
       </c>
       <c r="R56" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S56" s="7" t="s">
         <v>102</v>
@@ -12661,7 +12661,7 @@
         <v>12000</v>
       </c>
       <c r="R57" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S57" s="7" t="s">
         <v>102</v>
@@ -12712,7 +12712,7 @@
         <v>12000</v>
       </c>
       <c r="R58" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S58" s="7" t="s">
         <v>102</v>
@@ -12764,7 +12764,7 @@
         <v>12000</v>
       </c>
       <c r="R59" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S59" s="7" t="s">
         <v>102</v>
@@ -12816,7 +12816,7 @@
         <v>12000</v>
       </c>
       <c r="R60" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S60" s="7" t="s">
         <v>102</v>
@@ -12868,7 +12868,7 @@
         <v>12000</v>
       </c>
       <c r="R61" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S61" s="7" t="s">
         <v>102</v>
